--- a/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>HPQ</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>44865</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44135</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43769</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43404</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43039</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42674</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42308</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41943</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41578</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41213</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40847</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>53718000</v>
+      </c>
+      <c r="E8" s="3">
         <v>62910000</v>
       </c>
-      <c r="E8" s="3">
-        <v>63487000</v>
-      </c>
       <c r="F8" s="3">
+        <v>63460000</v>
+      </c>
+      <c r="G8" s="3">
         <v>56639000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>58756000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58472000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>52056000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>48238000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51463000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56651000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>112298000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>120357000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>127245000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42210000</v>
+      </c>
+      <c r="E9" s="3">
         <v>50647000</v>
       </c>
-      <c r="E9" s="3">
-        <v>50070000</v>
-      </c>
       <c r="F9" s="3">
+        <v>50053000</v>
+      </c>
+      <c r="G9" s="3">
         <v>46202000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47586000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>47803000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>42478000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39240000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>120120000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>130270000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>86380000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>92385000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>97418000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11508000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12263000</v>
       </c>
-      <c r="E10" s="3">
-        <v>13417000</v>
-      </c>
       <c r="F10" s="3">
+        <v>13407000</v>
+      </c>
+      <c r="G10" s="3">
         <v>10437000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11170000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10669000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9578000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8998000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-68657000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-73619000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25918000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27972000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29827000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,50 +875,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1578000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1653000</v>
       </c>
-      <c r="E12" s="3">
-        <v>1907000</v>
-      </c>
       <c r="F12" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="G12" s="3">
         <v>1478000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1499000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1404000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1190000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1209000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1191000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1298000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3135000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3399000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3254000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E14" s="3">
         <v>559000</v>
       </c>
-      <c r="E14" s="3">
-        <v>-1975000</v>
-      </c>
       <c r="F14" s="3">
+        <v>-1969000</v>
+      </c>
+      <c r="G14" s="3">
         <v>518000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>310000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>388000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>492000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>384000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1491000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>187000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1012000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>20346000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1712000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E15" s="3">
         <v>228000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>154000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>113000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>116000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>80000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>102000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>129000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1373000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1784000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1607000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>50155000</v>
+      </c>
+      <c r="E17" s="3">
         <v>58351000</v>
       </c>
-      <c r="E17" s="3">
-        <v>55897000</v>
-      </c>
       <c r="F17" s="3">
+        <v>55813000</v>
+      </c>
+      <c r="G17" s="3">
         <v>53217000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54879000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54767000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48688000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44689000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47543000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52395000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>105167000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>131414000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>117568000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3563000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4559000</v>
       </c>
-      <c r="E18" s="3">
-        <v>7590000</v>
-      </c>
       <c r="F18" s="3">
+        <v>7647000</v>
+      </c>
+      <c r="G18" s="3">
         <v>3422000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3877000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3705000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3368000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3549000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3920000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4256000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7131000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11057000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9677000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E20" s="3">
         <v>124000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>175000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>48000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1112000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-380000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>217000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>485000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-221000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-226000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-195000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-876000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-695000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4335000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5463000</v>
       </c>
-      <c r="E21" s="3">
-        <v>8550000</v>
-      </c>
       <c r="F21" s="3">
+        <v>8607000</v>
+      </c>
+      <c r="G21" s="3">
         <v>4259000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3509000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3853000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3939000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4366000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7760000</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="3">
         <v>-6838000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13966000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E22" s="3">
         <v>359000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>254000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>239000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>242000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>312000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>309000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>273000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>167000</v>
       </c>
       <c r="L22" s="3">
         <v>167000</v>
       </c>
       <c r="M22" s="3">
+        <v>167000</v>
+      </c>
+      <c r="N22" s="3">
         <v>426000</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2937000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4324000</v>
       </c>
-      <c r="E23" s="3">
-        <v>7511000</v>
-      </c>
       <c r="F23" s="3">
+        <v>7568000</v>
+      </c>
+      <c r="G23" s="3">
         <v>3231000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2523000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3013000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3276000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3761000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3532000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3863000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6510000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11933000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8982000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-326000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1192000</v>
       </c>
-      <c r="E24" s="3">
-        <v>1008000</v>
-      </c>
       <c r="F24" s="3">
+        <v>1027000</v>
+      </c>
+      <c r="G24" s="3">
         <v>387000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-551000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>150000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>750000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1095000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-186000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>939000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1397000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>717000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1908000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3132000</v>
       </c>
-      <c r="E26" s="3">
-        <v>6503000</v>
-      </c>
       <c r="F26" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="G26" s="3">
         <v>2844000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3074000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2863000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2526000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2666000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3718000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2924000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5113000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12650000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7074000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3132000</v>
       </c>
-      <c r="E27" s="3">
-        <v>6503000</v>
-      </c>
       <c r="F27" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="G27" s="3">
         <v>2844000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3074000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2863000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2526000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2666000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3718000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2924000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5113000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12650000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7074000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1537,29 +1597,29 @@
       <c r="E29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>78000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>2464000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-170000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>836000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>2089000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>17</v>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-124000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-175000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-48000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1112000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>380000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-217000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-485000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>221000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>226000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>195000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>876000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>695000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3132000</v>
       </c>
-      <c r="E33" s="3">
-        <v>6503000</v>
-      </c>
       <c r="F33" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="G33" s="3">
         <v>2844000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3152000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5327000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2526000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2496000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4554000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5013000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5113000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12650000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7074000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3132000</v>
       </c>
-      <c r="E35" s="3">
-        <v>6503000</v>
-      </c>
       <c r="F35" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="G35" s="3">
         <v>2844000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3152000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5327000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2526000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2496000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4554000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5013000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5113000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12650000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7074000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>44865</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44135</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43769</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43404</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43039</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42674</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42308</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41943</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41578</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41213</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40847</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,73 +1988,77 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3232000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3145000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4299000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4864000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4537000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5166000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6997000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6288000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7584000</v>
       </c>
       <c r="L41" s="3">
         <v>7584000</v>
       </c>
       <c r="M41" s="3">
+        <v>7584000</v>
+      </c>
+      <c r="N41" s="3">
         <v>12163000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11301000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8043000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>274000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>711000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1149000</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>17</v>
@@ -1986,177 +2075,192 @@
       <c r="O42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6438000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6891000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8849000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8443000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8939000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8003000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7162000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6609000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>10001000</v>
       </c>
       <c r="L43" s="3">
         <v>10001000</v>
       </c>
       <c r="M43" s="3">
+        <v>10001000</v>
+      </c>
+      <c r="N43" s="3">
         <v>24024000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25506000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29790000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6862000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7614000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7930000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5963000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5734000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6062000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5786000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4484000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>4288000</v>
       </c>
       <c r="L44" s="3">
         <v>4288000</v>
       </c>
       <c r="M44" s="3">
+        <v>4288000</v>
+      </c>
+      <c r="N44" s="3">
         <v>6046000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6317000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7490000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1445000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2086000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1087000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1104000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>967000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1445000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1224000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1087000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>32832000</v>
       </c>
       <c r="L45" s="3">
         <v>32832000</v>
       </c>
       <c r="M45" s="3">
+        <v>32832000</v>
+      </c>
+      <c r="N45" s="3">
         <v>8131000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11243000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8860000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17977000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19736000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22170000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20648000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20177000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21387000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22318000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18468000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>51787000</v>
       </c>
       <c r="L46" s="3">
         <v>51787000</v>
       </c>
       <c r="M46" s="3">
+        <v>51787000</v>
+      </c>
+      <c r="N46" s="3">
         <v>50364000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>50637000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51021000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2169,120 +2273,129 @@
       <c r="F47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="3">
         <v>144000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1042000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1793000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1607000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3724000</v>
       </c>
       <c r="L47" s="3">
         <v>3724000</v>
       </c>
       <c r="M47" s="3">
+        <v>3724000</v>
+      </c>
+      <c r="N47" s="3">
         <v>5274000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5924000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5916000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4015000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4010000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3738000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3734000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2794000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2198000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1878000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1736000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>10664000</v>
       </c>
       <c r="L48" s="3">
         <v>10664000</v>
       </c>
       <c r="M48" s="3">
+        <v>10664000</v>
+      </c>
+      <c r="N48" s="3">
         <v>11463000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11954000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12292000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10184000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12407000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7587000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6920000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7033000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5968000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>5622000</v>
       </c>
       <c r="J49" s="3">
         <v>5622000</v>
       </c>
       <c r="K49" s="3">
-        <v>7694000</v>
+        <v>5622000</v>
       </c>
       <c r="L49" s="3">
         <v>7694000</v>
       </c>
       <c r="M49" s="3">
+        <v>7694000</v>
+      </c>
+      <c r="N49" s="3">
         <v>34293000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>40563000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>51344000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4828000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4274000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5115000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3379000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3319000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4027000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1302000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1570000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>47923000</v>
       </c>
       <c r="L52" s="3">
         <v>47923000</v>
       </c>
       <c r="M52" s="3">
+        <v>47923000</v>
+      </c>
+      <c r="N52" s="3">
         <v>4282000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4669000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5457000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37004000</v>
+      </c>
+      <c r="E54" s="3">
         <v>38494000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38610000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34681000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33467000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34622000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32913000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28987000</v>
-      </c>
-      <c r="K54" s="3">
-        <v>106882000</v>
       </c>
       <c r="L54" s="3">
         <v>106882000</v>
       </c>
       <c r="M54" s="3">
+        <v>106882000</v>
+      </c>
+      <c r="N54" s="3">
         <v>105676000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108768000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>129517000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14046000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15303000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16075000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14704000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14793000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14816000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13279000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11103000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>10194000</v>
       </c>
       <c r="L57" s="3">
         <v>10194000</v>
       </c>
       <c r="M57" s="3">
+        <v>10194000</v>
+      </c>
+      <c r="N57" s="3">
         <v>14019000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13350000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14750000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E58" s="3">
         <v>218000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1106000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>674000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>357000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1463000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1072000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>78000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2233000</v>
       </c>
       <c r="L58" s="3">
         <v>2233000</v>
       </c>
       <c r="M58" s="3">
+        <v>2233000</v>
+      </c>
+      <c r="N58" s="3">
         <v>5979000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6647000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8083000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10212000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10668000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11915000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10842000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10143000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8852000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8061000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7627000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>30492000</v>
       </c>
       <c r="L59" s="3">
         <v>30492000</v>
       </c>
       <c r="M59" s="3">
+        <v>30492000</v>
+      </c>
+      <c r="N59" s="3">
         <v>25523000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32509000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27609000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24488000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26189000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29096000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26220000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25293000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25131000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22412000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18808000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>42191000</v>
       </c>
       <c r="L60" s="3">
         <v>42191000</v>
       </c>
       <c r="M60" s="3">
+        <v>42191000</v>
+      </c>
+      <c r="N60" s="3">
         <v>45521000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46666000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>50442000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9254000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10796000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6386000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5543000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4780000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4524000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6747000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6735000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>6677000</v>
       </c>
       <c r="L61" s="3">
         <v>6677000</v>
       </c>
       <c r="M61" s="3">
+        <v>6677000</v>
+      </c>
+      <c r="N61" s="3">
         <v>16608000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21789000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22551000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4331000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4534000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4778000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5146000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4587000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5606000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7162000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7333000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>7414000</v>
       </c>
       <c r="L62" s="3">
         <v>7414000</v>
       </c>
       <c r="M62" s="3">
+        <v>7414000</v>
+      </c>
+      <c r="N62" s="3">
         <v>15891000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20861000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17520000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38073000</v>
+      </c>
+      <c r="E66" s="3">
         <v>41519000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40260000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36909000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34660000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35261000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36321000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32876000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>79114000</v>
       </c>
       <c r="L66" s="3">
         <v>79114000</v>
       </c>
       <c r="M66" s="3">
+        <v>79114000</v>
+      </c>
+      <c r="N66" s="3">
         <v>78407000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>86332000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90892000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2361000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4492000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2461000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1961000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-818000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-473000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2386000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3498000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>32089000</v>
       </c>
       <c r="L72" s="3">
         <v>32089000</v>
       </c>
       <c r="M72" s="3">
+        <v>32089000</v>
+      </c>
+      <c r="N72" s="3">
         <v>25563000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21521000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35266000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1069000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3025000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1650000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2228000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1193000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-639000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-3408000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3889000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>27768000</v>
       </c>
       <c r="L76" s="3">
         <v>27768000</v>
       </c>
       <c r="M76" s="3">
+        <v>27768000</v>
+      </c>
+      <c r="N76" s="3">
         <v>27269000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22436000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38625000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>44865</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44135</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43769</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43404</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43039</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42674</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42308</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41943</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41578</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41213</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40847</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3132000</v>
       </c>
-      <c r="E81" s="3">
-        <v>6503000</v>
-      </c>
       <c r="F81" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="G81" s="3">
         <v>2844000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3152000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5327000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2526000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2496000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4554000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5013000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5113000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12650000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7074000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E83" s="3">
         <v>780000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>785000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>789000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>744000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>528000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>354000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>332000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4061000</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" s="3">
         <v>5095000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4984000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3571000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4463000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6409000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4316000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4654000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4528000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3677000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3252000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7026000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12333000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11608000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10571000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12639000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-609000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-791000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-582000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-580000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-671000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-546000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-402000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-433000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3603000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3853000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3199000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3706000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4539000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-590000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3549000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1012000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1016000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-438000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-716000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>48000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5534000</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O94" s="3">
         <v>-3453000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13959000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3999,41 +4232,44 @@
         <v>-1037000</v>
       </c>
       <c r="E96" s="3">
+        <v>-1037000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-938000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-997000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-970000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-899000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-894000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-858000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1250000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1184000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1105000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1015000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-844000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,51 +4399,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2894000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5962000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2973000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4845000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5643000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14445000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>808000</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O100" s="3">
         <v>-3860000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1566000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4229,61 +4477,67 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>17</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1154000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-565000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>327000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-629000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>709000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11145000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2300000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2970000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>862000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3258000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2886000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>HPQ</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44865</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44135</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43769</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43404</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43039</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42674</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42308</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41943</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41578</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41213</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40847</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>53559000</v>
+      </c>
+      <c r="E8" s="3">
         <v>53718000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62910000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63460000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56639000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58756000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58472000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>52056000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48238000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51463000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>56651000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>112298000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>120357000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>127245000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>41741000</v>
+      </c>
+      <c r="E9" s="3">
         <v>42210000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>50647000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50053000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46202000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>47586000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47803000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>42478000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39240000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>120120000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130270000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>86380000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>92385000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>97418000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11818000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11508000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12263000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13407000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10437000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11170000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10669000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9578000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8998000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-68657000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-73619000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25918000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27972000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29827000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,53 +888,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1640000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1578000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1653000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1848000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1478000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1499000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1404000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1190000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1209000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1191000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1298000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3135000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3399000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3254000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>660000</v>
+        <v>384000</v>
       </c>
       <c r="E14" s="3">
+        <v>799000</v>
+      </c>
+      <c r="F14" s="3">
         <v>559000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1969000</v>
       </c>
-      <c r="G14" s="3">
-        <v>518000</v>
-      </c>
       <c r="H14" s="3">
-        <v>310000</v>
+        <v>562000</v>
       </c>
       <c r="I14" s="3">
-        <v>388000</v>
+        <v>316000</v>
       </c>
       <c r="J14" s="3">
+        <v>381000</v>
+      </c>
+      <c r="K14" s="3">
         <v>492000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>384000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1491000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>187000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1012000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>20346000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1712000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E15" s="3">
         <v>350000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>228000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>154000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>113000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>116000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>80000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>102000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>129000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1373000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1784000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1607000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>50155000</v>
+        <v>49357000</v>
       </c>
       <c r="E17" s="3">
-        <v>58351000</v>
+        <v>49494000</v>
       </c>
       <c r="F17" s="3">
-        <v>55813000</v>
+        <v>57792000</v>
       </c>
       <c r="G17" s="3">
-        <v>53217000</v>
+        <v>57783000</v>
       </c>
       <c r="H17" s="3">
-        <v>54879000</v>
+        <v>52482000</v>
       </c>
       <c r="I17" s="3">
-        <v>54767000</v>
+        <v>54485000</v>
       </c>
       <c r="J17" s="3">
+        <v>54153000</v>
+      </c>
+      <c r="K17" s="3">
         <v>48688000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44689000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47543000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52395000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>105167000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>131414000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>117568000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3563000</v>
+        <v>4202000</v>
       </c>
       <c r="E18" s="3">
-        <v>4559000</v>
+        <v>4224000</v>
       </c>
       <c r="F18" s="3">
-        <v>7647000</v>
+        <v>5118000</v>
       </c>
       <c r="G18" s="3">
-        <v>3422000</v>
+        <v>5677000</v>
       </c>
       <c r="H18" s="3">
-        <v>3877000</v>
+        <v>4157000</v>
       </c>
       <c r="I18" s="3">
-        <v>3705000</v>
+        <v>4271000</v>
       </c>
       <c r="J18" s="3">
+        <v>4319000</v>
+      </c>
+      <c r="K18" s="3">
         <v>3368000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3549000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3920000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4256000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7131000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11057000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9677000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-78000</v>
       </c>
-      <c r="E20" s="3">
-        <v>124000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>175000</v>
-      </c>
       <c r="G20" s="3">
-        <v>48000</v>
+        <v>-145000</v>
       </c>
       <c r="H20" s="3">
-        <v>-1112000</v>
+        <v>165000</v>
       </c>
       <c r="I20" s="3">
-        <v>-380000</v>
+        <v>1270000</v>
       </c>
       <c r="J20" s="3">
+        <v>729000</v>
+      </c>
+      <c r="K20" s="3">
         <v>217000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>485000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-221000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-226000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-195000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-876000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-695000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>4335000</v>
+        <v>4520000</v>
       </c>
       <c r="E21" s="3">
-        <v>5463000</v>
+        <v>4567000</v>
       </c>
       <c r="F21" s="3">
-        <v>8607000</v>
+        <v>5424000</v>
       </c>
       <c r="G21" s="3">
-        <v>4259000</v>
+        <v>5976000</v>
       </c>
       <c r="H21" s="3">
-        <v>3509000</v>
+        <v>4105000</v>
       </c>
       <c r="I21" s="3">
-        <v>3853000</v>
+        <v>3117000</v>
       </c>
       <c r="J21" s="3">
+        <v>3670000</v>
+      </c>
+      <c r="K21" s="3">
         <v>3939000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4366000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7760000</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="3">
         <v>-6838000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13966000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>539000</v>
+      </c>
+      <c r="E22" s="3">
         <v>548000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>359000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>254000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>239000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>242000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>312000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>309000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>273000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>167000</v>
       </c>
       <c r="M22" s="3">
         <v>167000</v>
       </c>
       <c r="N22" s="3">
+        <v>167000</v>
+      </c>
+      <c r="O22" s="3">
         <v>426000</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3279000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2937000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4324000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7568000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3231000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2523000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3013000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3276000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3761000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3532000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3863000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6510000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11933000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8982000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-326000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1192000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1027000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>387000</v>
       </c>
-      <c r="H24" s="3">
-        <v>-551000</v>
-      </c>
       <c r="I24" s="3">
-        <v>150000</v>
+        <v>-629000</v>
       </c>
       <c r="J24" s="3">
+        <v>-2314000</v>
+      </c>
+      <c r="K24" s="3">
         <v>750000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1095000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-186000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>939000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1397000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>717000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1908000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3263000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3132000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6541000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2844000</v>
       </c>
-      <c r="H26" s="3">
-        <v>3074000</v>
-      </c>
       <c r="I26" s="3">
-        <v>2863000</v>
+        <v>3152000</v>
       </c>
       <c r="J26" s="3">
+        <v>5327000</v>
+      </c>
+      <c r="K26" s="3">
         <v>2526000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2666000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3718000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2924000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5113000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12650000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7074000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3263000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3132000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6541000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2844000</v>
       </c>
-      <c r="H27" s="3">
-        <v>3074000</v>
-      </c>
       <c r="I27" s="3">
-        <v>2863000</v>
+        <v>3152000</v>
       </c>
       <c r="J27" s="3">
+        <v>5327000</v>
+      </c>
+      <c r="K27" s="3">
         <v>2526000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2666000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3718000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2924000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5113000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12650000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7074000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,44 +1642,47 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>17</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>2464000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-170000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>836000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>2089000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>17</v>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>78000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-124000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-175000</v>
-      </c>
       <c r="G32" s="3">
-        <v>-48000</v>
+        <v>145000</v>
       </c>
       <c r="H32" s="3">
-        <v>1112000</v>
+        <v>-165000</v>
       </c>
       <c r="I32" s="3">
-        <v>380000</v>
+        <v>-1270000</v>
       </c>
       <c r="J32" s="3">
+        <v>-729000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-217000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-485000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>221000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>226000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>195000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>876000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>695000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3263000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3132000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6541000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2844000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3152000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5327000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2526000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2496000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4554000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5013000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5113000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12650000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7074000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3263000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3132000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6541000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2844000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3152000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5327000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2526000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2496000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4554000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5013000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5113000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12650000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7074000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44865</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44135</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43769</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43404</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43039</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42674</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42308</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41943</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41578</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41213</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40847</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,79 +2074,83 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3253000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3232000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3145000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4299000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4864000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4537000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5166000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6997000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6288000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>7584000</v>
       </c>
       <c r="M41" s="3">
         <v>7584000</v>
       </c>
       <c r="N41" s="3">
+        <v>7584000</v>
+      </c>
+      <c r="O41" s="3">
         <v>12163000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11301000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8043000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>17</v>
+      <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>274000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>278000</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>711000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1149000</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>17</v>
@@ -2078,324 +2167,348 @@
       <c r="P42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5117000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6438000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6891000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8849000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8443000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8939000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8003000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7162000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6609000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>10001000</v>
       </c>
       <c r="M43" s="3">
         <v>10001000</v>
       </c>
       <c r="N43" s="3">
+        <v>10001000</v>
+      </c>
+      <c r="O43" s="3">
         <v>24024000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25506000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29790000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7720000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6862000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7614000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7930000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5963000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5734000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6062000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5786000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4484000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>4288000</v>
       </c>
       <c r="M44" s="3">
         <v>4288000</v>
       </c>
       <c r="N44" s="3">
+        <v>4288000</v>
+      </c>
+      <c r="O44" s="3">
         <v>6046000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6317000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7490000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1445000</v>
+        <v>4667000</v>
       </c>
       <c r="E45" s="3">
-        <v>2086000</v>
+        <v>454000</v>
       </c>
       <c r="F45" s="3">
+        <v>868000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>278000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>226000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>324000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>408000</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1224000</v>
+      </c>
+      <c r="L45" s="3">
         <v>1087000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1104000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>967000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1445000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1224000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1087000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>32832000</v>
       </c>
       <c r="M45" s="3">
         <v>32832000</v>
       </c>
       <c r="N45" s="3">
+        <v>32832000</v>
+      </c>
+      <c r="O45" s="3">
         <v>8131000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11243000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8860000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20760000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17977000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19736000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22170000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20648000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20177000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21387000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22318000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18468000</v>
-      </c>
-      <c r="L46" s="3">
-        <v>51787000</v>
       </c>
       <c r="M46" s="3">
         <v>51787000</v>
       </c>
       <c r="N46" s="3">
+        <v>51787000</v>
+      </c>
+      <c r="O46" s="3">
         <v>50364000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>50637000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>51021000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>17</v>
+      <c r="E47" s="3">
+        <v>111000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>110000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>59000</v>
       </c>
       <c r="H47" s="3">
-        <v>144000</v>
+        <v>102000</v>
       </c>
       <c r="I47" s="3">
-        <v>1042000</v>
+        <v>60000</v>
       </c>
       <c r="J47" s="3">
+        <v>53000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1793000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1607000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>3724000</v>
       </c>
       <c r="M47" s="3">
         <v>3724000</v>
       </c>
       <c r="N47" s="3">
+        <v>3724000</v>
+      </c>
+      <c r="O47" s="3">
         <v>5274000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5924000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5916000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2914000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4015000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4010000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3738000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3734000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2794000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2198000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1878000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1736000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>10664000</v>
       </c>
       <c r="M48" s="3">
         <v>10664000</v>
       </c>
       <c r="N48" s="3">
+        <v>10664000</v>
+      </c>
+      <c r="O48" s="3">
         <v>11463000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11954000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12292000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8627000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10184000</v>
       </c>
-      <c r="E49" s="3">
-        <v>12407000</v>
-      </c>
       <c r="F49" s="3">
+        <v>10474000</v>
+      </c>
+      <c r="G49" s="3">
         <v>7587000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6920000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7033000</v>
       </c>
-      <c r="I49" s="3">
-        <v>5968000</v>
-      </c>
       <c r="J49" s="3">
-        <v>5622000</v>
+        <v>6421000</v>
       </c>
       <c r="K49" s="3">
         <v>5622000</v>
       </c>
       <c r="L49" s="3">
-        <v>7694000</v>
+        <v>5622000</v>
       </c>
       <c r="M49" s="3">
         <v>7694000</v>
       </c>
       <c r="N49" s="3">
+        <v>7694000</v>
+      </c>
+      <c r="O49" s="3">
         <v>34293000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>40563000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>51344000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4828000</v>
+        <v>7608000</v>
       </c>
       <c r="E52" s="3">
-        <v>4274000</v>
+        <v>1518000</v>
       </c>
       <c r="F52" s="3">
-        <v>5115000</v>
+        <v>1963000</v>
       </c>
       <c r="G52" s="3">
-        <v>3379000</v>
+        <v>2103000</v>
       </c>
       <c r="H52" s="3">
-        <v>3319000</v>
+        <v>728000</v>
       </c>
       <c r="I52" s="3">
-        <v>4027000</v>
+        <v>753000</v>
       </c>
       <c r="J52" s="3">
+        <v>2132000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1302000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1570000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>47923000</v>
       </c>
       <c r="M52" s="3">
         <v>47923000</v>
       </c>
       <c r="N52" s="3">
+        <v>47923000</v>
+      </c>
+      <c r="O52" s="3">
         <v>4282000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4669000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5457000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39909000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37004000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38494000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38610000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34681000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33467000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34622000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32913000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28987000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>106882000</v>
       </c>
       <c r="M54" s="3">
         <v>106882000</v>
       </c>
       <c r="N54" s="3">
+        <v>106882000</v>
+      </c>
+      <c r="O54" s="3">
         <v>105676000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108768000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>129517000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16903000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14046000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15303000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16075000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14704000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14793000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14816000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13279000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11103000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>10194000</v>
       </c>
       <c r="M57" s="3">
         <v>10194000</v>
       </c>
       <c r="N57" s="3">
+        <v>10194000</v>
+      </c>
+      <c r="O57" s="3">
         <v>14019000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13350000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14750000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>230000</v>
+        <v>1406000</v>
       </c>
       <c r="E58" s="3">
-        <v>218000</v>
+        <v>660000</v>
       </c>
       <c r="F58" s="3">
-        <v>1106000</v>
+        <v>623000</v>
       </c>
       <c r="G58" s="3">
-        <v>674000</v>
+        <v>1456000</v>
       </c>
       <c r="H58" s="3">
+        <v>949000</v>
+      </c>
+      <c r="I58" s="3">
         <v>357000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1463000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1072000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>78000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2233000</v>
       </c>
       <c r="M58" s="3">
         <v>2233000</v>
       </c>
       <c r="N58" s="3">
+        <v>2233000</v>
+      </c>
+      <c r="O58" s="3">
         <v>5979000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6647000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8083000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10212000</v>
+        <v>10378000</v>
       </c>
       <c r="E59" s="3">
-        <v>10668000</v>
+        <v>4689000</v>
       </c>
       <c r="F59" s="3">
-        <v>11915000</v>
+        <v>5261000</v>
       </c>
       <c r="G59" s="3">
-        <v>10842000</v>
+        <v>5532000</v>
       </c>
       <c r="H59" s="3">
-        <v>10143000</v>
+        <v>5137000</v>
       </c>
       <c r="I59" s="3">
-        <v>8852000</v>
+        <v>4619000</v>
       </c>
       <c r="J59" s="3">
+        <v>3976000</v>
+      </c>
+      <c r="K59" s="3">
         <v>8061000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7627000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>30492000</v>
       </c>
       <c r="M59" s="3">
         <v>30492000</v>
       </c>
       <c r="N59" s="3">
+        <v>30492000</v>
+      </c>
+      <c r="O59" s="3">
         <v>25523000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32509000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27609000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28687000</v>
+      </c>
+      <c r="E60" s="3">
         <v>24488000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26189000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29096000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26220000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25293000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25131000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22412000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18808000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>42191000</v>
       </c>
       <c r="M60" s="3">
         <v>42191000</v>
       </c>
       <c r="N60" s="3">
+        <v>42191000</v>
+      </c>
+      <c r="O60" s="3">
         <v>45521000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46666000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>50442000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9254000</v>
+        <v>8263000</v>
       </c>
       <c r="E61" s="3">
-        <v>10796000</v>
+        <v>10137000</v>
       </c>
       <c r="F61" s="3">
-        <v>6386000</v>
+        <v>11749000</v>
       </c>
       <c r="G61" s="3">
-        <v>5543000</v>
+        <v>7346000</v>
       </c>
       <c r="H61" s="3">
+        <v>6450000</v>
+      </c>
+      <c r="I61" s="3">
         <v>4780000</v>
       </c>
-      <c r="I61" s="3">
-        <v>4524000</v>
-      </c>
       <c r="J61" s="3">
+        <v>4547000</v>
+      </c>
+      <c r="K61" s="3">
         <v>6747000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6735000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>6677000</v>
       </c>
       <c r="M61" s="3">
         <v>6677000</v>
       </c>
       <c r="N61" s="3">
+        <v>6677000</v>
+      </c>
+      <c r="O61" s="3">
         <v>16608000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21789000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22551000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4331000</v>
+        <v>4282000</v>
       </c>
       <c r="E62" s="3">
-        <v>4534000</v>
+        <v>1535000</v>
       </c>
       <c r="F62" s="3">
-        <v>4778000</v>
+        <v>1689000</v>
       </c>
       <c r="G62" s="3">
-        <v>5146000</v>
+        <v>1621000</v>
       </c>
       <c r="H62" s="3">
-        <v>4587000</v>
+        <v>1566000</v>
       </c>
       <c r="I62" s="3">
-        <v>5606000</v>
+        <v>1696000</v>
       </c>
       <c r="J62" s="3">
+        <v>2833000</v>
+      </c>
+      <c r="K62" s="3">
         <v>7162000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7333000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>7414000</v>
       </c>
       <c r="M62" s="3">
         <v>7414000</v>
       </c>
       <c r="N62" s="3">
+        <v>7414000</v>
+      </c>
+      <c r="O62" s="3">
         <v>15891000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20861000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17520000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41232000</v>
+      </c>
+      <c r="E66" s="3">
         <v>38073000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41519000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40260000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36909000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34660000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35261000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36321000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32876000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>79114000</v>
       </c>
       <c r="M66" s="3">
         <v>79114000</v>
       </c>
       <c r="N66" s="3">
+        <v>79114000</v>
+      </c>
+      <c r="O66" s="3">
         <v>78407000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>86332000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90892000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2361000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4492000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2461000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1961000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-818000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-473000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2386000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3498000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>32089000</v>
       </c>
       <c r="M72" s="3">
         <v>32089000</v>
       </c>
       <c r="N72" s="3">
+        <v>32089000</v>
+      </c>
+      <c r="O72" s="3">
         <v>25563000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21521000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35266000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1323000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1069000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3025000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1650000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2228000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1193000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-639000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3408000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3889000</v>
-      </c>
-      <c r="L76" s="3">
-        <v>27768000</v>
       </c>
       <c r="M76" s="3">
         <v>27768000</v>
       </c>
       <c r="N76" s="3">
+        <v>27768000</v>
+      </c>
+      <c r="O76" s="3">
         <v>27269000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22436000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>38625000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44865</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44135</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43769</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43404</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43039</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42674</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42308</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41943</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41578</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41213</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40847</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3263000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3132000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6541000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2844000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3152000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5327000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2526000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2496000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4554000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5013000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5113000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12650000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7074000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>850000</v>
+        <v>512000</v>
       </c>
       <c r="E83" s="3">
-        <v>780000</v>
+        <v>500000</v>
       </c>
       <c r="F83" s="3">
-        <v>785000</v>
+        <v>552000</v>
       </c>
       <c r="G83" s="3">
-        <v>789000</v>
+        <v>631000</v>
       </c>
       <c r="H83" s="3">
-        <v>744000</v>
+        <v>676000</v>
       </c>
       <c r="I83" s="3">
-        <v>528000</v>
+        <v>628000</v>
       </c>
       <c r="J83" s="3">
+        <v>448000</v>
+      </c>
+      <c r="K83" s="3">
         <v>354000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>332000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4061000</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P83" s="3">
         <v>5095000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4984000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3749000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3571000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4463000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6409000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4316000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4654000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4528000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3677000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3252000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7026000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12333000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11608000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10571000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12639000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-592000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-609000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-791000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-582000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-580000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-671000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-546000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-402000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-433000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3603000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3853000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3199000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3706000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4539000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-646000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-590000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3549000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1012000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1016000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-438000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-716000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>48000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5534000</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3453000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13959000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1037000</v>
+        <v>1075000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1037000</v>
+        <v>1037000</v>
       </c>
       <c r="F96" s="3">
-        <v>-938000</v>
+        <v>1037000</v>
       </c>
       <c r="G96" s="3">
-        <v>-997000</v>
+        <v>938000</v>
       </c>
       <c r="H96" s="3">
-        <v>-970000</v>
+        <v>997000</v>
       </c>
       <c r="I96" s="3">
-        <v>-899000</v>
+        <v>970000</v>
       </c>
       <c r="J96" s="3">
+        <v>899000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-894000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-858000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1250000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1184000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1105000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1015000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-844000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,77 +4644,83 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3082000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2894000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5962000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2973000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4845000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5643000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14445000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>808000</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P100" s="3">
         <v>-3860000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1566000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4480,64 +4728,70 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>17</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>87000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1154000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-565000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>327000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-629000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>709000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11145000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2300000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2970000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>862000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3258000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2886000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>HPQ</t>
   </si>
@@ -991,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>384000</v>
+        <v>387000</v>
       </c>
       <c r="E14" s="3">
         <v>799000</v>
@@ -1104,13 +1104,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>49357000</v>
+        <v>49345000</v>
       </c>
       <c r="E17" s="3">
-        <v>49494000</v>
+        <v>49380000</v>
       </c>
       <c r="F17" s="3">
-        <v>57792000</v>
+        <v>57397000</v>
       </c>
       <c r="G17" s="3">
         <v>57783000</v>
@@ -1152,13 +1152,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>4202000</v>
+        <v>4214000</v>
       </c>
       <c r="E18" s="3">
-        <v>4224000</v>
+        <v>4338000</v>
       </c>
       <c r="F18" s="3">
-        <v>5118000</v>
+        <v>5513000</v>
       </c>
       <c r="G18" s="3">
         <v>5677000</v>
@@ -1219,14 +1219,14 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>17</v>
+      <c r="D20" s="3">
+        <v>174000</v>
       </c>
       <c r="E20" s="3">
-        <v>7000</v>
+        <v>121000</v>
       </c>
       <c r="F20" s="3">
-        <v>-78000</v>
+        <v>317000</v>
       </c>
       <c r="G20" s="3">
         <v>-145000</v>
@@ -1268,7 +1268,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>4520000</v>
+        <v>4358000</v>
       </c>
       <c r="E21" s="3">
         <v>4567000</v>
@@ -1316,7 +1316,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>539000</v>
+        <v>452000</v>
       </c>
       <c r="E22" s="3">
         <v>548000</v>
@@ -1795,14 +1795,14 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
+      <c r="D32" s="3">
+        <v>-174000</v>
       </c>
       <c r="E32" s="3">
-        <v>-7000</v>
+        <v>-121000</v>
       </c>
       <c r="F32" s="3">
-        <v>78000</v>
+        <v>-317000</v>
       </c>
       <c r="G32" s="3">
         <v>145000</v>
@@ -2129,7 +2129,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5117000</v>
+        <v>9477000</v>
       </c>
       <c r="E43" s="3">
         <v>6438000</v>
@@ -2273,7 +2273,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4667000</v>
+        <v>206000</v>
       </c>
       <c r="E45" s="3">
         <v>454000</v>
@@ -2368,8 +2368,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>17</v>
+      <c r="D47" s="3">
+        <v>111000</v>
       </c>
       <c r="E47" s="3">
         <v>111000</v>
@@ -2417,7 +2417,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2914000</v>
+        <v>4079000</v>
       </c>
       <c r="E48" s="3">
         <v>4015000</v>
@@ -2465,7 +2465,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8627000</v>
+        <v>9946000</v>
       </c>
       <c r="E49" s="3">
         <v>10184000</v>
@@ -2609,7 +2609,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7608000</v>
+        <v>1652000</v>
       </c>
       <c r="E52" s="3">
         <v>1518000</v>
@@ -2841,7 +2841,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1406000</v>
+        <v>1860000</v>
       </c>
       <c r="E58" s="3">
         <v>660000</v>
@@ -2889,7 +2889,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10378000</v>
+        <v>4661000</v>
       </c>
       <c r="E59" s="3">
         <v>4689000</v>
@@ -2985,7 +2985,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8263000</v>
+        <v>9061000</v>
       </c>
       <c r="E61" s="3">
         <v>10137000</v>
@@ -3033,10 +3033,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4282000</v>
+        <v>1359000</v>
       </c>
       <c r="E62" s="3">
-        <v>1535000</v>
+        <v>1534000</v>
       </c>
       <c r="F62" s="3">
         <v>1689000</v>
@@ -3484,8 +3484,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>17</v>
+      <c r="D72" s="3">
+        <v>-2676000</v>
       </c>
       <c r="E72" s="3">
         <v>-2361000</v>
@@ -4253,10 +4253,10 @@
         <v>-592000</v>
       </c>
       <c r="E91" s="3">
-        <v>-609000</v>
+        <v>-593000</v>
       </c>
       <c r="F91" s="3">
-        <v>-791000</v>
+        <v>-765000</v>
       </c>
       <c r="G91" s="3">
         <v>-582000</v>

--- a/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPQ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>HPQ</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44500</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44135</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43769</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43404</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43039</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42674</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42308</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41943</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41578</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41213</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40847</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55295000</v>
+      </c>
+      <c r="E8" s="3">
         <v>53559000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53718000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62910000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63460000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56639000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58756000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>58472000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>52056000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>48238000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51463000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>56651000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>112298000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>120357000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>127245000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43903000</v>
+      </c>
+      <c r="E9" s="3">
         <v>41741000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42210000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50647000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>50053000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>46202000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47586000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47803000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42478000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39240000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120120000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>130270000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>86380000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92385000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>97418000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11392000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11818000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11508000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12263000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13407000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10437000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11170000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10669000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9578000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8998000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-68657000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-73619000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25918000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27972000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29827000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,56 +901,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1602000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1640000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1578000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1653000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1848000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1478000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1499000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1404000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1190000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1209000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1191000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1298000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3135000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3399000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3254000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E14" s="3">
         <v>387000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>799000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>559000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1969000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>562000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>316000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>381000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>492000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>384000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1491000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>187000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1012000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>20346000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1712000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E15" s="3">
         <v>318000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>350000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>228000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>154000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>113000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>116000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>80000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>102000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>129000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1373000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1784000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1607000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>51645000</v>
+      </c>
+      <c r="E17" s="3">
         <v>49345000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>49380000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>57397000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>57783000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52482000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54485000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54153000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48688000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44689000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47543000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52395000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>105167000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131414000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>117568000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3650000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4214000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4338000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5513000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5677000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4157000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4271000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4319000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3368000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3549000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3920000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4256000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7131000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11057000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9677000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E20" s="3">
         <v>174000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>121000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>317000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-145000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>165000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1270000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>729000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>217000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>485000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-221000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-226000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-195000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-876000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-695000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3752000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4358000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4567000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5424000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5976000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4105000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3117000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3670000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3939000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4366000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7760000</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-6838000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13966000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E22" s="3">
         <v>452000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>548000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>359000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>254000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>239000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>242000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>312000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>309000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>273000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>167000</v>
       </c>
       <c r="N22" s="3">
         <v>167000</v>
       </c>
       <c r="O22" s="3">
+        <v>167000</v>
+      </c>
+      <c r="P22" s="3">
         <v>426000</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2668000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3279000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2937000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4324000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7568000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3231000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2523000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3013000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3276000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3761000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3532000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3863000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6510000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11933000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8982000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E24" s="3">
         <v>504000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-326000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1192000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1027000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>387000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-629000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2314000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>750000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1095000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-186000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>939000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1397000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>717000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1908000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2775000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3263000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3132000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6541000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2844000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3152000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5327000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2526000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2666000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3718000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2924000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5113000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12650000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7074000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2775000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3263000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3132000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6541000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2844000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3152000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5327000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2526000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2666000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3718000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2924000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5113000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12650000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7074000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,16 +1736,16 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-170000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>836000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>2089000</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>17</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-174000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-121000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-317000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>145000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-165000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1270000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-729000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-217000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-485000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>221000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>226000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>195000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>876000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>695000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2775000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3263000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3132000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6541000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2844000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3152000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5327000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2526000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2496000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4554000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5013000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5113000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12650000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7074000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2775000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3263000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3132000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6541000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2844000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3152000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5327000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2526000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2496000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4554000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5013000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5113000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12650000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7074000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44500</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44135</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43769</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43404</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43039</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42674</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42308</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41943</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41578</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41213</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40847</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3253000</v>
+        <v>3690000</v>
       </c>
       <c r="E41" s="3">
+        <v>3238000</v>
+      </c>
+      <c r="F41" s="3">
         <v>3232000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3145000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4299000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4864000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4537000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5166000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6997000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6288000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>7584000</v>
       </c>
       <c r="N41" s="3">
         <v>7584000</v>
       </c>
       <c r="O41" s="3">
+        <v>7584000</v>
+      </c>
+      <c r="P41" s="3">
         <v>12163000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11301000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8043000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,19 +2230,19 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>278000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>711000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1149000</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>17</v>
@@ -2170,345 +2259,369 @@
       <c r="Q42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9477000</v>
+        <v>8659000</v>
       </c>
       <c r="E43" s="3">
+        <v>8325000</v>
+      </c>
+      <c r="F43" s="3">
         <v>6438000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6891000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8849000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8443000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8939000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8003000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7162000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6609000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>10001000</v>
       </c>
       <c r="N43" s="3">
         <v>10001000</v>
       </c>
       <c r="O43" s="3">
+        <v>10001000</v>
+      </c>
+      <c r="P43" s="3">
         <v>24024000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25506000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29790000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8512000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7720000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6862000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7614000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7930000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5963000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5734000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6062000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5786000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4484000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>4288000</v>
       </c>
       <c r="N44" s="3">
         <v>4288000</v>
       </c>
       <c r="O44" s="3">
+        <v>4288000</v>
+      </c>
+      <c r="P44" s="3">
         <v>6046000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6317000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7490000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>206000</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3">
         <v>454000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>868000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>278000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>226000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>324000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>408000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1224000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1087000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>32832000</v>
       </c>
       <c r="N45" s="3">
         <v>32832000</v>
       </c>
       <c r="O45" s="3">
+        <v>32832000</v>
+      </c>
+      <c r="P45" s="3">
         <v>8131000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11243000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8860000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22453000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20760000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17977000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19736000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22170000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20648000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20177000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21387000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22318000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18468000</v>
-      </c>
-      <c r="M46" s="3">
-        <v>51787000</v>
       </c>
       <c r="N46" s="3">
         <v>51787000</v>
       </c>
       <c r="O46" s="3">
+        <v>51787000</v>
+      </c>
+      <c r="P46" s="3">
         <v>50364000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>50637000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51021000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3">
         <v>111000</v>
       </c>
-      <c r="E47" s="3">
-        <v>111000</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>110000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>102000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>60000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>53000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1793000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1607000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>3724000</v>
       </c>
       <c r="N47" s="3">
         <v>3724000</v>
       </c>
       <c r="O47" s="3">
+        <v>3724000</v>
+      </c>
+      <c r="P47" s="3">
         <v>5274000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5924000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5916000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4178000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4079000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4015000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4010000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3738000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3734000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2794000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2198000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1878000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1736000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>10664000</v>
       </c>
       <c r="N48" s="3">
         <v>10664000</v>
       </c>
       <c r="O48" s="3">
+        <v>10664000</v>
+      </c>
+      <c r="P48" s="3">
         <v>11463000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11954000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12292000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9718000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9946000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10184000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10474000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7587000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6920000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7033000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6421000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>5622000</v>
       </c>
       <c r="L49" s="3">
         <v>5622000</v>
       </c>
       <c r="M49" s="3">
-        <v>7694000</v>
+        <v>5622000</v>
       </c>
       <c r="N49" s="3">
         <v>7694000</v>
       </c>
       <c r="O49" s="3">
+        <v>7694000</v>
+      </c>
+      <c r="P49" s="3">
         <v>34293000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>40563000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>51344000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1652000</v>
+        <v>2102000</v>
       </c>
       <c r="E52" s="3">
+        <v>1813000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1518000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1963000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2103000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>728000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>753000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2132000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1302000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1570000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>47923000</v>
       </c>
       <c r="N52" s="3">
         <v>47923000</v>
       </c>
       <c r="O52" s="3">
+        <v>47923000</v>
+      </c>
+      <c r="P52" s="3">
         <v>4282000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4669000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5457000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41769000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39909000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37004000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38494000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38610000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34681000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33467000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>34622000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32913000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28987000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>106882000</v>
       </c>
       <c r="N54" s="3">
         <v>106882000</v>
       </c>
       <c r="O54" s="3">
+        <v>106882000</v>
+      </c>
+      <c r="P54" s="3">
         <v>105676000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108768000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>129517000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18051000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16903000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14046000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15303000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16075000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14704000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14793000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14816000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13279000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11103000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>10194000</v>
       </c>
       <c r="N57" s="3">
         <v>10194000</v>
       </c>
       <c r="O57" s="3">
+        <v>10194000</v>
+      </c>
+      <c r="P57" s="3">
         <v>14019000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13350000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14750000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1860000</v>
+        <v>1246000</v>
       </c>
       <c r="E58" s="3">
+        <v>1849000</v>
+      </c>
+      <c r="F58" s="3">
         <v>660000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>623000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1456000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>949000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>357000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1463000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1072000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>78000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2233000</v>
       </c>
       <c r="N58" s="3">
         <v>2233000</v>
       </c>
       <c r="O58" s="3">
+        <v>2233000</v>
+      </c>
+      <c r="P58" s="3">
         <v>5979000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6647000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8083000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4661000</v>
+        <v>4635000</v>
       </c>
       <c r="E59" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="F59" s="3">
         <v>4689000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5261000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5532000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5137000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4619000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3976000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8061000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7627000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>30492000</v>
       </c>
       <c r="N59" s="3">
         <v>30492000</v>
       </c>
       <c r="O59" s="3">
+        <v>30492000</v>
+      </c>
+      <c r="P59" s="3">
         <v>25523000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32509000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27609000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29258000</v>
+      </c>
+      <c r="E60" s="3">
         <v>28687000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24488000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26189000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29096000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26220000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25293000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25131000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22412000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18808000</v>
-      </c>
-      <c r="M60" s="3">
-        <v>42191000</v>
       </c>
       <c r="N60" s="3">
         <v>42191000</v>
       </c>
       <c r="O60" s="3">
+        <v>42191000</v>
+      </c>
+      <c r="P60" s="3">
         <v>45521000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46666000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>50442000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9061000</v>
+        <v>9636000</v>
       </c>
       <c r="E61" s="3">
+        <v>9050000</v>
+      </c>
+      <c r="F61" s="3">
         <v>10137000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11749000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7346000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6450000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4780000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4547000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6747000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6735000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>6677000</v>
       </c>
       <c r="N61" s="3">
         <v>6677000</v>
       </c>
       <c r="O61" s="3">
+        <v>6677000</v>
+      </c>
+      <c r="P61" s="3">
         <v>16608000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21789000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22551000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1359000</v>
+        <v>1009000</v>
       </c>
       <c r="E62" s="3">
+        <v>1370000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1534000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1689000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1621000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1566000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1696000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2833000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7162000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7333000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>7414000</v>
       </c>
       <c r="N62" s="3">
         <v>7414000</v>
       </c>
       <c r="O62" s="3">
+        <v>7414000</v>
+      </c>
+      <c r="P62" s="3">
         <v>15891000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20861000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17520000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42115000</v>
+      </c>
+      <c r="E66" s="3">
         <v>41232000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38073000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41519000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40260000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36909000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34660000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35261000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36321000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32876000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>79114000</v>
       </c>
       <c r="N66" s="3">
         <v>79114000</v>
       </c>
       <c r="O66" s="3">
+        <v>79114000</v>
+      </c>
+      <c r="P66" s="3">
         <v>78407000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>86332000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90892000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2027000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2676000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2361000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4492000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2461000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1961000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-818000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-473000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2386000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3498000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>32089000</v>
       </c>
       <c r="N72" s="3">
         <v>32089000</v>
       </c>
       <c r="O72" s="3">
+        <v>32089000</v>
+      </c>
+      <c r="P72" s="3">
         <v>25563000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21521000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>35266000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1323000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1069000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3025000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1650000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2228000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1193000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-639000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3408000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3889000</v>
-      </c>
-      <c r="M76" s="3">
-        <v>27768000</v>
       </c>
       <c r="N76" s="3">
         <v>27768000</v>
       </c>
       <c r="O76" s="3">
+        <v>27768000</v>
+      </c>
+      <c r="P76" s="3">
         <v>27269000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22436000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38625000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44500</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44135</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43769</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43404</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43039</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42674</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42308</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41943</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41578</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41213</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40847</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2775000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3263000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3132000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6541000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2844000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3152000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5327000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2526000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2496000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4554000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5013000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5113000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12650000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7074000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E83" s="3">
         <v>512000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>552000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>631000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>676000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>628000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>448000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>354000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>332000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4061000</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5095000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4984000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3697000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3749000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3571000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4463000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6409000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4316000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4654000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4528000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3677000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3252000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7026000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12333000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11608000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10571000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12639000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-897000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-592000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-593000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-765000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-582000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-580000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-671000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-546000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-402000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-433000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3603000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3853000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3199000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3706000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4539000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1177000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-646000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-590000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3549000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1012000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1016000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-438000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-716000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>48000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5534000</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-3453000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13959000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1088000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1075000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>1037000</v>
       </c>
       <c r="F96" s="3">
         <v>1037000</v>
       </c>
       <c r="G96" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="H96" s="3">
         <v>938000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>997000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>970000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>899000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-894000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-858000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1250000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1184000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1105000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1015000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-844000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2060000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3082000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2894000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5962000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2973000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4845000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5643000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14445000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>808000</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-3860000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1566000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4722,8 +4970,8 @@
       <c r="J101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4731,67 +4979,73 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>17</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E102" s="3">
         <v>21000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1154000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-565000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>327000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-629000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1831000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>709000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11145000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2300000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2970000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>862000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3258000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2886000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
